--- a/results/abnmac/abnmac_classC_Ru20_Rv40_SC/classC_Ru20_Rv40_SC.xlsx
+++ b/results/abnmac/abnmac_classC_Ru20_Rv40_SC/classC_Ru20_Rv40_SC.xlsx
@@ -473,7 +473,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ABN-MAC — Class C, (Ru=0.20, Rv=0.40), SC (L=1), analytic design</t>
+          <t>ABN-MAC — Class C, (Ru=0.20, Rv=0.40), SC (L=1)</t>
         </is>
       </c>
     </row>
